--- a/monily-package/Monily_Tax_Package_2025.xlsx
+++ b/monily-package/Monily_Tax_Package_2025.xlsx
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>-53544.62</v>
+        <v>-86531.81</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>-53544.62</v>
+        <v>-86531.81</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>8253.410000000003</v>
+        <v>-24733.78</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>48028.41</v>
+        <v>15041.22</v>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>85996.83</v>
+        <v>34188.88</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>47241.05901639345</v>
+        <v>14794.64262295082</v>
       </c>
     </row>
     <row r="23">
@@ -828,7 +828,7 @@
         <v>946.97</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>393.6754918032788</v>
+        <v>123.2886885245902</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         <v>946.97</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>393.6754918032788</v>
+        <v>123.2886885245902</v>
       </c>
     </row>
     <row r="26">
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4152.7</v>
+        <v>37139.89</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>4152.7</v>
+        <v>37139.89</v>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>53544.62</v>
+        <v>86531.81</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>53544.62</v>
+        <v>86531.81</v>
       </c>
       <c r="D16" s="16" t="inlineStr"/>
     </row>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>-53544.62</v>
+        <v>-86531.81</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>-53544.62</v>
+        <v>-86531.81</v>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
     </row>
@@ -1408,10 +1408,10 @@
         <v/>
       </c>
       <c r="B33" s="10" t="n">
-        <v>8253.410000000003</v>
+        <v>-24733.78</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>48028.41</v>
+        <v>15041.22</v>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>85996.83</v>
+        <v>34188.88</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>85996.83</v>
+        <v>34188.88</v>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>8118.108196721315</v>
+        <v>-24328.30819672131</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>47241.05901639345</v>
+        <v>14794.64262295082</v>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>67.6509016393443</v>
+        <v>-202.7359016393443</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>393.6754918032788</v>
+        <v>123.2886885245902</v>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>67.6509016393443</v>
+        <v>-202.7359016393443</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>393.6754918032788</v>
+        <v>123.2886885245902</v>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>-85996.83</v>
+        <v>-34188.88</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Fund Mgmt $85,049.86 + direct $946.97</t>
+          <t>Fund Mgmt $33,241.91 + direct $946.97</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>8253.410000000003</v>
+        <v>-24733.78</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>GAAP: $8,253.41. Reclass: $48,028.41</t>
+          <t>GAAP: $-24,733.78. Reclass: $15,041.22</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="B26" s="15" t="n">
-        <v>-79637.36</v>
+        <v>-60816.6</v>
       </c>
       <c r="C26" s="14" t="inlineStr"/>
       <c r="D26" s="16" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>-79637.36</v>
+        <v>-60816.6</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" s="8" t="inlineStr">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>119412.36</v>
+        <v>100591.6</v>
       </c>
       <c r="C31" s="17" t="inlineStr"/>
       <c r="D31" s="18" t="inlineStr">
@@ -2098,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G7" s="7" t="n">
-        <v>335.47</v>
+        <v>1743.04</v>
       </c>
     </row>
     <row r="8">
@@ -2306,16 +2306,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>Raj Duggal</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (Fund Mgmt 59.5% slice)</t>
+          <t>Distribution to Raj Duggal (direct 0.5%)</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>2815.16</v>
+        <v>255.92</v>
       </c>
     </row>
     <row r="11">
@@ -2336,16 +2336,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Raj Duggal</t>
+          <t>Nairne</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Distribution to Raj Duggal (direct 0.5%)</t>
+          <t>Distribution to Nairne (direct 0.5%)</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>255.92</v>
+        <v>1663.5</v>
       </c>
     </row>
     <row r="12">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (direct 0.5%)</t>
+          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
@@ -2386,26 +2386,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>506c SPV Loan (RECLASS to Asset)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>506c SPV Loan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
+          <t>GP-paid expense: 506c SPV Loan</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>255.92</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="14">
@@ -2421,51 +2421,51 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>506c SPV Loan (RECLASS to Asset)</t>
+          <t>Professional Fees — PVD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>506c SPV Loan</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GP-paid expense: 506c SPV Loan</t>
+          <t>GP-paid expense: PVD</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>4275</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Professional Fees — PVD</t>
+          <t>Performance Fees Income</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>Armada Prime LLP (TPA)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GP-paid expense: PVD</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>6000</v>
+          <t>Sep 2025 GP cut received from fund</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>12474.75</v>
       </c>
     </row>
     <row r="16">
@@ -2476,26 +2476,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Performance Fees Income</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Armada Prime LLP (TPA)</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sep 2025 GP cut received from fund</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>12474.75</v>
+          <t>1099-NEC payment to AJ Affleck</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>6068.58</v>
       </c>
     </row>
     <row r="17">
@@ -2516,16 +2516,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1099-NEC payment to AJ Affleck</t>
+          <t>1099-NEC payment to Alec Atkinson</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>285.77</v>
+        <v>3561.92</v>
       </c>
     </row>
     <row r="18">
@@ -2546,16 +2546,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Alec Atkinson</t>
+          <t>1099-NEC payment to Jake Gordon</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>3561.92</v>
+        <v>930.9</v>
       </c>
     </row>
     <row r="19">
@@ -2566,26 +2566,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Raj Duggal</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Jake Gordon</t>
+          <t>Distribution to Raj Duggal (direct 0.5%)</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>930.9</v>
+        <v>62.32</v>
       </c>
     </row>
     <row r="20">
@@ -2611,11 +2611,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (Fund Mgmt 59.5% slice)</t>
+          <t>Distribution to Nairne (direct 0.5%)</t>
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>7415.62</v>
+        <v>5845.12</v>
       </c>
     </row>
     <row r="21">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Raj Duggal</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Distribution to Raj Duggal (direct 0.5%)</t>
+          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
@@ -2651,61 +2651,61 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Performance Fees Income</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>Armada Prime LLP (TPA)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (direct 0.5%)</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>62.32</v>
+          <t>Oct 2025 GP cut received from fund</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>51906.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
+          <t>1099-NEC payment to AJ Affleck</t>
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>62.32</v>
+        <v>7500.6</v>
       </c>
     </row>
     <row r="24">
@@ -2716,26 +2716,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Performance Fees Income</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Armada Prime LLP (TPA)</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oct 2025 GP cut received from fund</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>51906.99</v>
+          <t>1099-NEC payment to Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>11848.88</v>
       </c>
     </row>
     <row r="25">
@@ -2756,16 +2756,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1099-NEC payment to AJ Affleck</t>
+          <t>1099-NEC payment to Jake Gordon</t>
         </is>
       </c>
       <c r="G25" s="7" t="n">
-        <v>1268.23</v>
+        <v>3218.29</v>
       </c>
     </row>
     <row r="26">
@@ -2786,16 +2786,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Issac</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Alec Atkinson</t>
+          <t>1099-NEC payment to Issac</t>
         </is>
       </c>
       <c r="G26" s="7" t="n">
-        <v>11848.88</v>
+        <v>254.12</v>
       </c>
     </row>
     <row r="27">
@@ -2806,26 +2806,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Raj Duggal</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Jake Gordon</t>
+          <t>Distribution to Raj Duggal (direct 0.5%)</t>
         </is>
       </c>
       <c r="G27" s="7" t="n">
-        <v>3218.29</v>
+        <v>262.24</v>
       </c>
     </row>
     <row r="28">
@@ -2836,26 +2836,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>Nairne</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Issac</t>
+          <t>Distribution to Nairne (direct 0.5%)</t>
         </is>
       </c>
       <c r="G28" s="7" t="n">
-        <v>254.12</v>
+        <v>6244.65</v>
       </c>
     </row>
     <row r="29">
@@ -2876,16 +2876,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (Fund Mgmt 59.5% slice)</t>
+          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
         </is>
       </c>
       <c r="G29" s="7" t="n">
-        <v>31206.94</v>
+        <v>262.24</v>
       </c>
     </row>
     <row r="30">
@@ -2896,26 +2896,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>506c SPV Loan (RECLASS to Asset)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Raj Duggal</t>
+          <t>506c SPV Loan</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Distribution to Raj Duggal (direct 0.5%)</t>
+          <t>GP-paid expense: 506c SPV Loan</t>
         </is>
       </c>
       <c r="G30" s="7" t="n">
-        <v>262.24</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="31">
@@ -2926,26 +2926,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Professional Fees — PVD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (direct 0.5%)</t>
+          <t>GP-paid expense: PVD</t>
         </is>
       </c>
       <c r="G31" s="7" t="n">
-        <v>262.24</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="32">
@@ -2956,26 +2956,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Marketing — Website</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
+          <t>GP-paid expense: Website</t>
         </is>
       </c>
       <c r="G32" s="7" t="n">
-        <v>262.24</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="33">
@@ -2991,57 +2991,57 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>506c SPV Loan (RECLASS to Asset)</t>
+          <t>Marketing — Advertising</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>506c SPV Loan</t>
+          <t>Ad Spend</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GP-paid expense: 506c SPV Loan</t>
+          <t>GP-paid expense: Ad Spend</t>
         </is>
       </c>
       <c r="G33" s="7" t="n">
-        <v>25000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Professional Fees — PVD</t>
+          <t>Performance Fees Income</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>Armada Prime LLP (TPA)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GP-paid expense: PVD</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>6000</v>
+          <t>Nov 2025 GP cut received from fund</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>57074.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3051,27 +3051,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Marketing — Website</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GP-paid expense: Website</t>
+          <t>1099-NEC payment to AJ Affleck</t>
         </is>
       </c>
       <c r="G35" s="7" t="n">
-        <v>7500</v>
+        <v>16567.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3081,21 +3081,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Marketing — Advertising</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ad Spend</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GP-paid expense: Ad Spend</t>
+          <t>1099-NEC payment to Alec Atkinson</t>
         </is>
       </c>
       <c r="G36" s="7" t="n">
-        <v>5000</v>
+        <v>15124.18</v>
       </c>
     </row>
     <row r="37">
@@ -3106,26 +3106,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Performance Fees Income</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Armada Prime LLP (TPA)</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nov 2025 GP cut received from fund</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>57074.09</v>
+          <t>1099-NEC payment to Jake Gordon</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>4184.51</v>
       </c>
     </row>
     <row r="38">
@@ -3146,16 +3146,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Issac</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1099-NEC payment to AJ Affleck</t>
+          <t>1099-NEC payment to Issac</t>
         </is>
       </c>
       <c r="G38" s="7" t="n">
-        <v>1833.52</v>
+        <v>785.85</v>
       </c>
     </row>
     <row r="39">
@@ -3166,26 +3166,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Raj Duggal</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Alec Atkinson</t>
+          <t>Distribution to Raj Duggal (direct 0.5%)</t>
         </is>
       </c>
       <c r="G39" s="7" t="n">
-        <v>15124.18</v>
+        <v>287.26</v>
       </c>
     </row>
     <row r="40">
@@ -3196,26 +3196,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Nairne</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Jake Gordon</t>
+          <t>Distribution to Nairne (direct 0.5%)</t>
         </is>
       </c>
       <c r="G40" s="7" t="n">
-        <v>4184.51</v>
+        <v>15531.01</v>
       </c>
     </row>
     <row r="41">
@@ -3226,26 +3226,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Issac</t>
+          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
         </is>
       </c>
       <c r="G41" s="7" t="n">
-        <v>785.85</v>
+        <v>287.26</v>
       </c>
     </row>
     <row r="42">
@@ -3256,26 +3256,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Contractor Labor — Chris</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (Fund Mgmt 59.5% slice)</t>
+          <t>GP-paid expense: Chris</t>
         </is>
       </c>
       <c r="G42" s="7" t="n">
-        <v>34183.9</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="43">
@@ -3286,26 +3286,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Compliance — Verification</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Raj Duggal</t>
+          <t>Alpha Verification</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Distribution to Raj Duggal (direct 0.5%)</t>
+          <t>GP-paid expense: Alpha Verification</t>
         </is>
       </c>
       <c r="G43" s="7" t="n">
-        <v>287.26</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="44">
@@ -3316,62 +3316,62 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Professional Fees — TPA Admin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>Formidium (TPA)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (direct 0.5%)</t>
+          <t>GP-paid expense: Formidium (TPA)</t>
         </is>
       </c>
       <c r="G44" s="7" t="n">
-        <v>287.26</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Performance Fees Income</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Armada Prime LLP (TPA)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>287.26</v>
+          <t>Dec 2025 GP cut received from fund</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>16211.69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3381,27 +3381,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Contractor Labor — Chris</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>GP-paid expense: Chris</t>
+          <t>1099-NEC payment to AJ Affleck</t>
         </is>
       </c>
       <c r="G46" s="7" t="n">
-        <v>7500</v>
+        <v>5260.51</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3411,27 +3411,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Compliance — Verification</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Alpha Verification</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GP-paid expense: Alpha Verification</t>
+          <t>1099-NEC payment to Alec Atkinson</t>
         </is>
       </c>
       <c r="G47" s="7" t="n">
-        <v>2250</v>
+        <v>4369.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3441,21 +3441,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Professional Fees — TPA Admin</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Formidium (TPA)</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>GP-paid expense: Formidium (TPA)</t>
+          <t>1099-NEC payment to Jake Gordon</t>
         </is>
       </c>
       <c r="G48" s="7" t="n">
-        <v>600</v>
+        <v>788.78</v>
       </c>
     </row>
     <row r="49">
@@ -3466,26 +3466,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Performance Fees Income</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Armada Prime LLP (TPA)</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dec 2025 GP cut received from fund</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>16211.69</v>
+          <t>1099-NEC payment to Luke</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>164.9</v>
       </c>
     </row>
     <row r="50">
@@ -3506,16 +3506,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Issac</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1099-NEC payment to AJ Affleck</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>429.71</v>
+          <t>1099-NEC payment to Issac</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>278.48</v>
       </c>
     </row>
     <row r="51">
@@ -3526,26 +3526,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Raj Duggal</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Alec Atkinson</t>
+          <t>Distribution to Raj Duggal (direct 0.5%)</t>
         </is>
       </c>
       <c r="G51" s="7" t="n">
-        <v>4369.77</v>
+        <v>79.23</v>
       </c>
     </row>
     <row r="52">
@@ -3556,26 +3556,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Nairne</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Jake Gordon</t>
+          <t>Distribution to Nairne (direct 0.5%)</t>
         </is>
       </c>
       <c r="G52" s="7" t="n">
-        <v>788.78</v>
+        <v>4904.6</v>
       </c>
     </row>
     <row r="53">
@@ -3586,26 +3586,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Luke</t>
+          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
         </is>
       </c>
       <c r="G53" s="7" t="n">
-        <v>164.9</v>
+        <v>79.23</v>
       </c>
     </row>
     <row r="54">
@@ -3621,21 +3621,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>Contractor Labor — Chris</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Issac</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>278.48</v>
+          <t>GP-paid expense: Chris</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="55">
@@ -3646,26 +3646,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Professional Fees — TPA Admin</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>TPA (Formidium)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (Fund Mgmt 59.5% slice)</t>
+          <t>GP-paid expense: TPA (Formidium)</t>
         </is>
       </c>
       <c r="G55" s="7" t="n">
-        <v>9428.24</v>
+        <v>600</v>
       </c>
     </row>
     <row r="56">
@@ -3676,26 +3676,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Insurance Expense</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Raj Duggal</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Distribution to Raj Duggal (direct 0.5%)</t>
+          <t>GP-paid expense: Insurance</t>
         </is>
       </c>
       <c r="G56" s="7" t="n">
-        <v>79.23</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="57">
@@ -3706,280 +3706,130 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Professional Fees — TPA Admin</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>TPA (second line)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (direct 0.5%)</t>
+          <t>GP-paid expense: TPA (second line)</t>
         </is>
       </c>
       <c r="G57" s="7" t="n">
-        <v>79.23</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Distribution</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>K-1 Distribution to Member</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Phil</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>79.23</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="20" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Contractor Labor — Chris</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Chris</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>GP-paid expense: Chris</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>4000</v>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL TRANSACTIONS: 52</t>
+        </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Professional Fees — TPA Admin</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>TPA (Formidium)</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>GP-paid expense: TPA (Formidium)</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="n">
-        <v>600</v>
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL DEBITS</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="n">
+        <v>153301.51</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="20" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Insurance Expense</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>GP-paid expense: Insurance</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="n">
-        <v>18000</v>
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL CREDITS</t>
+        </is>
+      </c>
+      <c r="G61" s="21" t="n">
+        <v>214118.1100000001</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="20" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Professional Fees — TPA Admin</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>TPA (second line)</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>GP-paid expense: TPA (second line)</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>4500</v>
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>NET (Debit − Credit) = Net Income proxy: $-60,816.60</t>
+        </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL TRANSACTIONS: 57</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL DEBITS</t>
-        </is>
-      </c>
-      <c r="F65" s="21" t="n">
-        <v>153301.51</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL CREDITS</t>
-        </is>
-      </c>
-      <c r="G66" s="21" t="n">
-        <v>232938.8700000001</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="22" t="inlineStr">
-        <is>
-          <t>NET (Debit − Credit) = Net Income proxy: $-79,637.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="23" t="inlineStr">
+      <c r="A64" s="23" t="inlineStr">
         <is>
           <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Each row = one cash transaction. Revenue receipts are debits to Cash; distributions and expense payments are credits to Cash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>K-1 Distribution to Member: Nairne, Raj, Phil (all K-1 partners).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>Capital Raiser Commission Expense: Alec, Jake, AJ, Issac, Luke (1099 contractors).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Dates are end-of-month. Actual settlement may have been days/weeks later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Source: Distributions Armada Tech 2025 ledger + BEST ONE Dec 2025 Costs.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>Each row = one cash transaction. Revenue receipts are debits to Cash; distributions and expense payments are credits to Cash.</t>
+          <t>TruQuant payments excluded entirely (per Nairne 2026-04-30).</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member: Nairne, Raj, Phil (all K-1 partners).</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>Capital Raiser Commission Expense: Alec, Jake, AJ, Issac, Luke (1099 contractors).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>Dates are end-of-month. Actual settlement may have been days/weeks later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>Source: Distributions Armada Tech 2025 ledger + BEST ONE Dec 2025 Costs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>TruQuant payments excluded entirely (per Nairne 2026-04-30).</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
           <t>Issac's December −$278.48 entry is a clawback against prior month overpayment.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A66:G66"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A74:G74"/>
     <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A67:G67"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A69:G69"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A73:G73"/>
     <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A68:G68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4280,13 +4130,13 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>85996.83</v>
+        <v>34188.88</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>8118.108196721315</v>
+        <v>-24328.30819672131</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>47241.05901639345</v>
+        <v>14794.64262295082</v>
       </c>
       <c r="F8" s="12" t="inlineStr"/>
     </row>
@@ -4305,10 +4155,10 @@
         <v>946.97</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>67.6509016393443</v>
+        <v>-202.7359016393443</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>393.6754918032788</v>
+        <v>123.2886885245902</v>
       </c>
       <c r="F9" s="12" t="inlineStr"/>
     </row>
@@ -4327,10 +4177,10 @@
         <v>946.97</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>67.6509016393443</v>
+        <v>-202.7359016393443</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>393.6754918032788</v>
+        <v>123.2886885245902</v>
       </c>
       <c r="F10" s="12" t="inlineStr"/>
     </row>
@@ -4346,13 +4196,13 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>87890.77</v>
+        <v>36082.82</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>8253.410000000003</v>
+        <v>-24733.78</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>48028.41000000001</v>
+        <v>15041.22</v>
       </c>
       <c r="F11" s="9" t="n"/>
     </row>
@@ -4511,7 +4361,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>4152.7</v>
+        <v>37139.89</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -4579,7 +4429,7 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>65044.62</v>
+        <v>98031.81</v>
       </c>
       <c r="C12" s="9" t="n"/>
       <c r="D12" s="9" t="n"/>

--- a/monily-package/Monily_Tax_Package_2025.xlsx
+++ b/monily-package/Monily_Tax_Package_2025.xlsx
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>-86531.81</v>
+        <v>-86754.81</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>-86531.81</v>
+        <v>-86754.81</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>-24733.78</v>
+        <v>-24956.78</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>15041.22</v>
+        <v>14818.22</v>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>34188.88</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>14794.64262295082</v>
+        <v>14575.29836065574</v>
       </c>
     </row>
     <row r="23">
@@ -828,7 +828,7 @@
         <v>946.97</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>123.2886885245902</v>
+        <v>121.4608196721312</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         <v>946.97</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>123.2886885245902</v>
+        <v>121.4608196721312</v>
       </c>
     </row>
     <row r="26">
@@ -986,7 +986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1175,384 +1175,394 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Nikki</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>223</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>223</v>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>1099-NEC issued separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Total Direct Costs</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
-        <v>86531.81</v>
-      </c>
-      <c r="C16" s="15" t="n">
-        <v>86531.81</v>
-      </c>
-      <c r="D16" s="16" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B17" s="15" t="n">
+        <v>86754.81</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>86754.81</v>
+      </c>
+      <c r="D17" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>OPERATING EXPENSES</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Chris (Contractor labor — 1099)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>11500</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>11500</v>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Issue 1099-NEC; verify SSN/address</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Insurance (D&amp;O)</t>
+          <t xml:space="preserve">  Chris (Contractor labor — 1099)</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>18000</v>
+        <v>11500</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>7500</v>
+        <v>11500</v>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Reclass: $18k Dec is annual D&amp;O. Pro-rate to ~$7,500 for Aug-Dec period.</t>
+          <t>Issue 1099-NEC; verify SSN/address</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PVD</t>
+          <t xml:space="preserve">  Insurance (D&amp;O)</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>12000</v>
+        <v>7500</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Vendor identification needed for 1099 obligation</t>
+          <t>Reclass: $18k Dec is annual D&amp;O. Pro-rate to ~$7,500 for Aug-Dec period.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Website</t>
+          <t xml:space="preserve">  PVD</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>7500</v>
+        <v>12000</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>7500</v>
+        <v>12000</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Marketing/web build</t>
+          <t>Vendor identification needed for 1099 obligation</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ad Spend / Marketing</t>
+          <t xml:space="preserve">  Website</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Marketing/web build</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Alpha Verification</t>
+          <t xml:space="preserve">  Ad Spend / Marketing</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>2250</v>
+        <v>5000</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>2250</v>
+        <v>5000</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Compliance/verification service</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TPA Admin Fees (Formidium)</t>
+          <t xml:space="preserve">  Alpha Verification</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>5700</v>
+        <v>2250</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>5700</v>
+        <v>2250</v>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Verify GP-paid vs fund-paid (fund books also have $600/mo)</t>
+          <t>Compliance/verification service</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t xml:space="preserve">  TPA Admin Fees (Formidium)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>5700</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>5700</v>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Verify GP-paid vs fund-paid (fund books also have $600/mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t xml:space="preserve">  506c SPV Loan</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B27" s="7" t="n">
         <v>29275</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>RECLASS to Balance Sheet: $29,275 is a loan/capital item, not P&amp;L expense.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
+      <c r="B28" s="15" t="n">
         <v>91225</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C28" s="15" t="n">
         <v>51450</v>
       </c>
-      <c r="D27" s="16" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>NET INCOME (Partnership)</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n">
-        <v>153023.03</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>153023.03</v>
-      </c>
-      <c r="D30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Less: Direct Costs (1099 contractors)</t>
+          <t>Total Revenue</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>-86531.81</v>
+        <v>153023.03</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>-86531.81</v>
+        <v>153023.03</v>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Less: Direct Costs (1099 contractors)</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>-86754.81</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>-86754.81</v>
+      </c>
+      <c r="D32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Less: Operating Expenses</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
+      <c r="B33" s="7" t="n">
         <v>-91225</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="7" t="n">
         <v>-51450</v>
       </c>
-      <c r="D32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9">
+      <c r="D33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9">
         <f> NET INCOME</f>
         <v/>
       </c>
-      <c r="B33" s="10" t="n">
-        <v>-24733.78</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>15041.22</v>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="B34" s="10" t="n">
+        <v>-24956.78</v>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>14818.22</v>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Tax-reclass column reflects accountant-preferred adjustments.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>K-1 PARTNER ALLOCATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Nairne — Cash distributions received</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="n">
-        <v>34188.88</v>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>34188.88</v>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Includes Fund Mgmt 59.5% + direct 0.5%. K-1 capital account.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nairne — Allocated share of Net Income (98.36%)</t>
+          <t>Nairne — Cash distributions received</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>-24328.30819672131</v>
+        <v>34188.88</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>14794.64262295082</v>
+        <v>34188.88</v>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>K-1 Box 1 (Ordinary Income).</t>
+          <t>Includes Fund Mgmt 59.5% + direct 0.5%. K-1 capital account.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Raj Duggal — Cash distributions received</t>
+          <t>Nairne — Allocated share of Net Income (98.36%)</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>946.97</v>
+        <v>-24547.65245901639</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>946.97</v>
+        <v>14575.29836065574</v>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>K-1 capital account.</t>
+          <t>K-1 Box 1 (Ordinary Income).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Raj Duggal — Allocated share of Net Income (0.82%)</t>
+          <t>Raj Duggal — Cash distributions received</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>-202.7359016393443</v>
+        <v>946.97</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>123.2886885245902</v>
+        <v>946.97</v>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>K-1 Box 1.</t>
+          <t>K-1 capital account.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Phil — Cash distributions received</t>
+          <t>Raj Duggal — Allocated share of Net Income (0.82%)</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>946.97</v>
+        <v>-204.5637704918033</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>946.97</v>
+        <v>121.4608196721312</v>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>K-1 capital account.</t>
+          <t>K-1 Box 1.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Phil — Cash distributions received</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>946.97</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>946.97</v>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>K-1 capital account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Phil — Allocated share of Net Income (0.82%)</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
-        <v>-202.7359016393443</v>
-      </c>
-      <c r="C41" s="7" t="n">
-        <v>123.2886885245902</v>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="B42" s="7" t="n">
+        <v>-204.5637704918033</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>121.4608196721312</v>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>K-1 Box 1.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>PREPARER NOTES</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>1. Entity formed at the Armada Prime relaunch in August 2025; first year of operations.</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2. Revenue source: TPA (Formidium) Performance Fees Crystallized line, Aug-Dec 2025.</t>
+          <t>1. Entity formed at the Armada Prime relaunch in August 2025; first year of operations.</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr"/>
@@ -1560,7 +1570,7 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3. Member structure (per Nairne 2026-05-05): Nairne 60% (Fund Mgmt 59.5% + direct 0.5%), Raj Duggal 0.5%, Phil 0.5%. All three are K-1 partners.</t>
+          <t>2. Revenue source: TPA (Formidium) Performance Fees Crystallized line, Aug-Dec 2025.</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr"/>
@@ -1568,7 +1578,7 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4. Phil was previously thought to be a 1099 contractor but has been corrected to K-1 partner status.</t>
+          <t>3. Member structure (per Nairne 2026-05-05): Nairne 60% (Fund Mgmt 59.5% + direct 0.5%), Raj Duggal 0.5%, Phil 0.5%. All three are K-1 partners.</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr"/>
@@ -1576,7 +1586,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5. TruQuant payments are NOT included. The August 'Trader &amp; Developer' $6,909.93 + 'Spydr' $88.78 are excluded per 2026-04-30 policy decision (TQ is upstream of GP entity).</t>
+          <t>4. Phil was previously thought to be a 1099 contractor but has been corrected to K-1 partner status.</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr"/>
@@ -1584,7 +1594,7 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6. Contractor amounts shown are CASH BASIS per Distributions Armada Tech 2025 ledger. Difference vs accrual basis (TPA Performance Fees Crystallized) ≈ $11,587.</t>
+          <t>5. TruQuant payments are NOT included. The August 'Trader &amp; Developer' $6,909.93 + 'Spydr' $88.78 are excluded per 2026-04-30 policy decision (TQ is upstream of GP entity).</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr"/>
@@ -1592,7 +1602,7 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7. RECOMMEND: $29,275 of '506c SPV Loan' line items should be reclassified to Balance Sheet (loan/capital).</t>
+          <t>6. Contractor amounts shown are CASH BASIS per Distributions Armada Tech 2025 ledger. Difference vs accrual basis (TPA Performance Fees Crystallized) ≈ $11,587.</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr"/>
@@ -1600,22 +1610,30 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
+          <t>7. RECOMMEND: $29,275 of '506c SPV Loan' line items should be reclassified to Balance Sheet (loan/capital).</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>8. RECOMMEND: $18,000 December Insurance line is likely annual D&amp;O — pro-rate to ~$7,500 for the 5-month period; book remainder as Prepaid Asset.</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr"/>
+      <c r="D52" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1949,7 +1967,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>-24733.78</v>
+        <v>-24956.78</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1958,7 +1976,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>GAAP: $-24,733.78. Reclass: $15,041.22</t>
+          <t>GAAP: $-24,956.78. Reclass: $14,818.22</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1987,7 @@
         </is>
       </c>
       <c r="B26" s="15" t="n">
-        <v>-60816.6</v>
+        <v>-61039.6</v>
       </c>
       <c r="C26" s="14" t="inlineStr"/>
       <c r="D26" s="16" t="inlineStr"/>
@@ -2000,7 +2018,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>-60816.6</v>
+        <v>-61039.6</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" s="8" t="inlineStr">
@@ -2016,7 +2034,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>100591.6</v>
+        <v>100814.6</v>
       </c>
       <c r="C31" s="17" t="inlineStr"/>
       <c r="D31" s="18" t="inlineStr">
@@ -2098,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3261,21 +3279,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Contractor Labor — Chris</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GP-paid expense: Chris</t>
+          <t>1099-NEC payment to Nikki</t>
         </is>
       </c>
       <c r="G42" s="7" t="n">
-        <v>7500</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43">
@@ -3291,21 +3309,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Compliance — Verification</t>
+          <t>Contractor Labor — Chris</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Alpha Verification</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GP-paid expense: Alpha Verification</t>
+          <t>GP-paid expense: Chris</t>
         </is>
       </c>
       <c r="G43" s="7" t="n">
-        <v>2250</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="44">
@@ -3321,51 +3339,51 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Professional Fees — TPA Admin</t>
+          <t>Compliance — Verification</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Formidium (TPA)</t>
+          <t>Alpha Verification</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GP-paid expense: Formidium (TPA)</t>
+          <t>GP-paid expense: Alpha Verification</t>
         </is>
       </c>
       <c r="G44" s="7" t="n">
-        <v>600</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Performance Fees Income</t>
+          <t>Professional Fees — TPA Admin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Armada Prime LLP (TPA)</t>
+          <t>Formidium (TPA)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dec 2025 GP cut received from fund</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>16211.69</v>
+          <t>GP-paid expense: Formidium (TPA)</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="46">
@@ -3376,26 +3394,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>Performance Fees Income</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Armada Prime LLP (TPA)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1099-NEC payment to AJ Affleck</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>5260.51</v>
+          <t>Dec 2025 GP cut received from fund</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>16211.69</v>
       </c>
     </row>
     <row r="47">
@@ -3416,16 +3434,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Alec Atkinson</t>
+          <t>1099-NEC payment to AJ Affleck</t>
         </is>
       </c>
       <c r="G47" s="7" t="n">
-        <v>4369.77</v>
+        <v>5260.51</v>
       </c>
     </row>
     <row r="48">
@@ -3446,16 +3464,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Jake Gordon</t>
+          <t>1099-NEC payment to Alec Atkinson</t>
         </is>
       </c>
       <c r="G48" s="7" t="n">
-        <v>788.78</v>
+        <v>4369.77</v>
       </c>
     </row>
     <row r="49">
@@ -3476,16 +3494,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Luke</t>
+          <t>1099-NEC payment to Jake Gordon</t>
         </is>
       </c>
       <c r="G49" s="7" t="n">
-        <v>164.9</v>
+        <v>788.78</v>
       </c>
     </row>
     <row r="50">
@@ -3506,16 +3524,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Issac</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>278.48</v>
+          <t>1099-NEC payment to Luke</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>164.9</v>
       </c>
     </row>
     <row r="51">
@@ -3526,26 +3544,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Raj Duggal</t>
+          <t>Issac</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Distribution to Raj Duggal (direct 0.5%)</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>79.23</v>
+          <t>1099-NEC payment to Issac</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>278.48</v>
       </c>
     </row>
     <row r="52">
@@ -3566,16 +3584,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>Raj Duggal</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (direct 0.5%)</t>
+          <t>Distribution to Raj Duggal (direct 0.5%)</t>
         </is>
       </c>
       <c r="G52" s="7" t="n">
-        <v>4904.6</v>
+        <v>79.23</v>
       </c>
     </row>
     <row r="53">
@@ -3596,16 +3614,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Nairne</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
+          <t>Distribution to Nairne (direct 0.5%)</t>
         </is>
       </c>
       <c r="G53" s="7" t="n">
-        <v>79.23</v>
+        <v>4904.6</v>
       </c>
     </row>
     <row r="54">
@@ -3616,26 +3634,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Contractor Labor — Chris</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GP-paid expense: Chris</t>
+          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
         </is>
       </c>
       <c r="G54" s="7" t="n">
-        <v>4000</v>
+        <v>79.23</v>
       </c>
     </row>
     <row r="55">
@@ -3651,21 +3669,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Professional Fees — TPA Admin</t>
+          <t>Contractor Labor — Chris</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TPA (Formidium)</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GP-paid expense: TPA (Formidium)</t>
+          <t>GP-paid expense: Chris</t>
         </is>
       </c>
       <c r="G55" s="7" t="n">
-        <v>600</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="56">
@@ -3681,21 +3699,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Insurance Expense</t>
+          <t>Professional Fees — TPA Admin</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>TPA (Formidium)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GP-paid expense: Insurance</t>
+          <t>GP-paid expense: TPA (Formidium)</t>
         </is>
       </c>
       <c r="G56" s="7" t="n">
-        <v>18000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="57">
@@ -3711,108 +3729,138 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>Insurance Expense</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>GP-paid expense: Insurance</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>Professional Fees — TPA Admin</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>TPA (second line)</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>GP-paid expense: TPA (second line)</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n">
+      <c r="G58" s="7" t="n">
         <v>4500</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL TRANSACTIONS: 52</t>
-        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>TOTAL DEBITS</t>
-        </is>
-      </c>
-      <c r="F60" s="21" t="n">
-        <v>153301.51</v>
+          <t>TOTAL TRANSACTIONS: 53</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
+          <t>TOTAL DEBITS</t>
+        </is>
+      </c>
+      <c r="F61" s="21" t="n">
+        <v>153301.51</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
           <t>TOTAL CREDITS</t>
         </is>
       </c>
-      <c r="G61" s="21" t="n">
-        <v>214118.1100000001</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="22" t="inlineStr">
-        <is>
-          <t>NET (Debit − Credit) = Net Income proxy: $-60,816.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="23" t="inlineStr">
+      <c r="G62" s="21" t="n">
+        <v>214341.1100000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>NET (Debit − Credit) = Net Income proxy: $-61,039.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="23" t="inlineStr">
         <is>
           <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>Each row = one cash transaction. Revenue receipts are debits to Cash; distributions and expense payments are credits to Cash.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member: Nairne, Raj, Phil (all K-1 partners).</t>
+          <t>Each row = one cash transaction. Revenue receipts are debits to Cash; distributions and expense payments are credits to Cash.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense: Alec, Jake, AJ, Issac, Luke (1099 contractors).</t>
+          <t>K-1 Distribution to Member: Nairne, Raj, Phil (all K-1 partners).</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>Dates are end-of-month. Actual settlement may have been days/weeks later.</t>
+          <t>Capital Raiser Commission Expense: Alec, Jake, AJ, Issac, Luke (1099 contractors).</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>Source: Distributions Armada Tech 2025 ledger + BEST ONE Dec 2025 Costs.</t>
+          <t>Dates are end-of-month. Actual settlement may have been days/weeks later.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>TruQuant payments excluded entirely (per Nairne 2026-04-30).</t>
+          <t>Source: Distributions Armada Tech 2025 ledger + BEST ONE Dec 2025 Costs.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>TruQuant payments excluded entirely (per Nairne 2026-04-30).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>Issac's December −$278.48 entry is a clawback against prior month overpayment.</t>
         </is>
@@ -3827,8 +3875,8 @@
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A69:G69"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A72:G72"/>
     <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A65:G65"/>
     <mergeCell ref="A68:G68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4133,10 +4181,10 @@
         <v>34188.88</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>-24328.30819672131</v>
+        <v>-24547.65245901639</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>14794.64262295082</v>
+        <v>14575.29836065574</v>
       </c>
       <c r="F8" s="12" t="inlineStr"/>
     </row>
@@ -4155,10 +4203,10 @@
         <v>946.97</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>-202.7359016393443</v>
+        <v>-204.5637704918033</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>123.2886885245902</v>
+        <v>121.4608196721312</v>
       </c>
       <c r="F9" s="12" t="inlineStr"/>
     </row>
@@ -4177,10 +4225,10 @@
         <v>946.97</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>-202.7359016393443</v>
+        <v>-204.5637704918033</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>123.2886885245902</v>
+        <v>121.4608196721312</v>
       </c>
       <c r="F10" s="12" t="inlineStr"/>
     </row>
@@ -4199,10 +4247,10 @@
         <v>36082.82</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>-24733.78</v>
+        <v>-24956.78</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>15041.22</v>
+        <v>14818.22</v>
       </c>
       <c r="F11" s="9" t="n"/>
     </row>
@@ -4262,7 +4310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4408,132 +4456,149 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chris (last name TBD)</t>
+          <t>Nikki (last name TBD)</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>11500</v>
+        <v>223</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Operating contractor labor (Nov $7,500 + Dec $4,000)</t>
+          <t>Capital raiser commission (Nov 2025 only)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chris (last name TBD)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>11500</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Operating contractor labor (Nov $7,500 + Dec $4,000)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>TOTAL 1099 PAYMENTS</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v>98031.81</v>
-      </c>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="B13" s="10" t="n">
+        <v>98254.81</v>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>VENDORS THAT MAY ALSO REQUIRE 1099</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>If individual/sole prop and &gt;$600 → 1099-NEC. Verify entity type.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ad Spend / Marketing vendors</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>If individual/sole prop. Verify.</t>
+          <t>If individual/sole prop and &gt;$600 → 1099-NEC. Verify entity type.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Website builder</t>
+          <t>Ad Spend / Marketing vendors</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>If individual contractor. Verify.</t>
+          <t>If individual/sole prop. Verify.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alpha Verification</t>
+          <t>Website builder</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>2250</v>
+        <v>7500</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Likely corporate; unlikely 1099 needed. Verify.</t>
+          <t>If individual contractor. Verify.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Insurance carrier</t>
+          <t>Alpha Verification</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>18000</v>
+        <v>2250</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Corporate — no 1099.</t>
+          <t>Likely corporate; unlikely 1099 needed. Verify.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Insurance carrier</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Corporate — no 1099.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Formidium (TPA)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B21" s="7" t="n">
         <v>5700</v>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Corporate — no 1099.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>NOTE: Phil is NOT on this 1099 list — Phil is a K-1 partner (per Nairne 2026-05-05). See K-1 Partners tab.</t>
         </is>
@@ -4542,8 +4607,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A22:E22"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/monily-package/Monily_Tax_Package_2025.xlsx
+++ b/monily-package/Monily_Tax_Package_2025.xlsx
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-05</t>
+          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-07</t>
         </is>
       </c>
     </row>
@@ -737,14 +737,14 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>-91225</v>
+        <v>-55225</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>-51450</v>
+        <v>-40450</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Reclass moves $29,275 SPV loans to balance sheet, pro-rates Insurance</t>
+          <t>Reclass moves $4,275 SPV loans to balance sheet, pro-rates Insurance</t>
         </is>
       </c>
     </row>
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>-24956.78</v>
+        <v>11043.22</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>14818.22</v>
+        <v>25818.22</v>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>34188.88</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>14575.29836065574</v>
+        <v>25394.97049180328</v>
       </c>
     </row>
     <row r="23">
@@ -828,7 +828,7 @@
         <v>946.97</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>121.4608196721312</v>
+        <v>211.6247540983607</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         <v>946.97</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>121.4608196721312</v>
+        <v>211.6247540983607</v>
       </c>
     </row>
     <row r="26">
@@ -1012,7 +1012,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-05</t>
+          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-07</t>
         </is>
       </c>
     </row>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>11500</v>
+        <v>4000</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>11500</v>
+        <v>4000</v>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
@@ -1346,14 +1346,14 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>29275</v>
+        <v>4275</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>RECLASS to Balance Sheet: $29,275 is a loan/capital item, not P&amp;L expense.</t>
+          <t>RECLASS to Balance Sheet: $4,275 is a loan/capital item, not P&amp;L expense.</t>
         </is>
       </c>
     </row>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="B28" s="15" t="n">
-        <v>91225</v>
+        <v>55225</v>
       </c>
       <c r="C28" s="15" t="n">
-        <v>51450</v>
+        <v>40450</v>
       </c>
       <c r="D28" s="16" t="inlineStr"/>
     </row>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>-91225</v>
+        <v>-55225</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>-51450</v>
+        <v>-40450</v>
       </c>
       <c r="D33" s="8" t="inlineStr"/>
     </row>
@@ -1426,10 +1426,10 @@
         <v/>
       </c>
       <c r="B34" s="10" t="n">
-        <v>-24956.78</v>
+        <v>11043.22</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>14818.22</v>
+        <v>25818.22</v>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>-24547.65245901639</v>
+        <v>10862.18360655738</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>14575.29836065574</v>
+        <v>25394.97049180328</v>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>-204.5637704918033</v>
+        <v>90.51819672131148</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>121.4608196721312</v>
+        <v>211.6247540983607</v>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>-204.5637704918033</v>
+        <v>90.51819672131148</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>121.4608196721312</v>
+        <v>211.6247540983607</v>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7. RECOMMEND: $29,275 of '506c SPV Loan' line items should be reclassified to Balance Sheet (loan/capital).</t>
+          <t>7. RECOMMEND: $4,275 of '506c SPV Loan' line items should be reclassified to Balance Sheet (loan/capital).</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-05</t>
+          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-07</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>29275</v>
+        <v>4275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>39775</v>
+        <v>14775</v>
       </c>
       <c r="C11" s="14" t="inlineStr"/>
       <c r="D11" s="16" t="inlineStr"/>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>-24956.78</v>
+        <v>11043.22</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>GAAP: $-24,956.78. Reclass: $14,818.22</t>
+          <t>GAAP: $11,043.22. Reclass: $25,818.22</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="B26" s="15" t="n">
-        <v>-61039.6</v>
+        <v>-25039.6</v>
       </c>
       <c r="C26" s="14" t="inlineStr"/>
       <c r="D26" s="16" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>39775</v>
+        <v>14775</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" s="8" t="inlineStr"/>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>-61039.6</v>
+        <v>-25039.6</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" s="8" t="inlineStr">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>100814.6</v>
+        <v>39814.6</v>
       </c>
       <c r="C31" s="17" t="inlineStr"/>
       <c r="D31" s="18" t="inlineStr">
@@ -2062,7 +2062,7 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2. 506c SPV Loans ($29,275) reclassified from P&amp;L to assets.</t>
+          <t>2. 506c SPV Loans ($4,275) reclassified from P&amp;L to assets.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -2116,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2145,7 +2145,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-05</t>
+          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2919,57 +2919,57 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>506c SPV Loan (RECLASS to Asset)</t>
+          <t>Marketing — Website</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>506c SPV Loan</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GP-paid expense: 506c SPV Loan</t>
+          <t>GP-paid expense: Website</t>
         </is>
       </c>
       <c r="G30" s="7" t="n">
-        <v>25000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Professional Fees — PVD</t>
+          <t>Performance Fees Income</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>Armada Prime LLP (TPA)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GP-paid expense: PVD</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>6000</v>
+          <t>Nov 2025 GP cut received from fund</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>57074.09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2979,27 +2979,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Marketing — Website</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GP-paid expense: Website</t>
+          <t>1099-NEC payment to AJ Affleck</t>
         </is>
       </c>
       <c r="G32" s="7" t="n">
-        <v>7500</v>
+        <v>16567.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3009,21 +3009,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Marketing — Advertising</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ad Spend</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GP-paid expense: Ad Spend</t>
+          <t>1099-NEC payment to Alec Atkinson</t>
         </is>
       </c>
       <c r="G33" s="7" t="n">
-        <v>5000</v>
+        <v>15124.18</v>
       </c>
     </row>
     <row r="34">
@@ -3034,26 +3034,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Performance Fees Income</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Armada Prime LLP (TPA)</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nov 2025 GP cut received from fund</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>57074.09</v>
+          <t>1099-NEC payment to Jake Gordon</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>4184.51</v>
       </c>
     </row>
     <row r="35">
@@ -3074,16 +3074,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Issac</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1099-NEC payment to AJ Affleck</t>
+          <t>1099-NEC payment to Issac</t>
         </is>
       </c>
       <c r="G35" s="7" t="n">
-        <v>16567.16</v>
+        <v>785.85</v>
       </c>
     </row>
     <row r="36">
@@ -3094,26 +3094,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Raj Duggal</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Alec Atkinson</t>
+          <t>Distribution to Raj Duggal (direct 0.5%)</t>
         </is>
       </c>
       <c r="G36" s="7" t="n">
-        <v>15124.18</v>
+        <v>287.26</v>
       </c>
     </row>
     <row r="37">
@@ -3124,26 +3124,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Nairne</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Jake Gordon</t>
+          <t>Distribution to Nairne (direct 0.5%)</t>
         </is>
       </c>
       <c r="G37" s="7" t="n">
-        <v>4184.51</v>
+        <v>15531.01</v>
       </c>
     </row>
     <row r="38">
@@ -3154,26 +3154,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Issac</t>
+          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
         </is>
       </c>
       <c r="G38" s="7" t="n">
-        <v>785.85</v>
+        <v>287.26</v>
       </c>
     </row>
     <row r="39">
@@ -3184,26 +3184,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Raj Duggal</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Distribution to Raj Duggal (direct 0.5%)</t>
+          <t>1099-NEC payment to Nikki</t>
         </is>
       </c>
       <c r="G39" s="7" t="n">
-        <v>287.26</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40">
@@ -3214,26 +3214,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Other Operating Expense</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (direct 0.5%)</t>
+          <t>GP-paid expense: Consulting</t>
         </is>
       </c>
       <c r="G40" s="7" t="n">
-        <v>15531.01</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="41">
@@ -3244,26 +3244,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Compliance — Verification</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Alpha Verification</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
+          <t>GP-paid expense: Alpha Verification</t>
         </is>
       </c>
       <c r="G41" s="7" t="n">
-        <v>287.26</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="42">
@@ -3279,57 +3279,57 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>Professional Fees — TPA Admin</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Formidium (TPA)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Nikki</t>
+          <t>GP-paid expense: Formidium (TPA)</t>
         </is>
       </c>
       <c r="G42" s="7" t="n">
-        <v>223</v>
+        <v>600</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Contractor Labor — Chris</t>
+          <t>Performance Fees Income</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Armada Prime LLP (TPA)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GP-paid expense: Chris</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>7500</v>
+          <t>Dec 2025 GP cut received from fund</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>16211.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3339,27 +3339,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Compliance — Verification</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Alpha Verification</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GP-paid expense: Alpha Verification</t>
+          <t>1099-NEC payment to AJ Affleck</t>
         </is>
       </c>
       <c r="G44" s="7" t="n">
-        <v>2250</v>
+        <v>5260.51</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3369,21 +3369,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Professional Fees — TPA Admin</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Formidium (TPA)</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GP-paid expense: Formidium (TPA)</t>
+          <t>1099-NEC payment to Alec Atkinson</t>
         </is>
       </c>
       <c r="G45" s="7" t="n">
-        <v>600</v>
+        <v>4369.77</v>
       </c>
     </row>
     <row r="46">
@@ -3394,26 +3394,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Performance Fees Income</t>
+          <t>Capital Raiser Commission Expense (1099)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Armada Prime LLP (TPA)</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dec 2025 GP cut received from fund</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>16211.69</v>
+          <t>1099-NEC payment to Jake Gordon</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>788.78</v>
       </c>
     </row>
     <row r="47">
@@ -3434,16 +3434,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1099-NEC payment to AJ Affleck</t>
+          <t>1099-NEC payment to Luke</t>
         </is>
       </c>
       <c r="G47" s="7" t="n">
-        <v>5260.51</v>
+        <v>164.9</v>
       </c>
     </row>
     <row r="48">
@@ -3464,16 +3464,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Issac</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Alec Atkinson</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>4369.77</v>
+          <t>1099-NEC payment to Issac</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>278.48</v>
       </c>
     </row>
     <row r="49">
@@ -3484,26 +3484,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Raj Duggal</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Jake Gordon</t>
+          <t>Distribution to Raj Duggal (direct 0.5%)</t>
         </is>
       </c>
       <c r="G49" s="7" t="n">
-        <v>788.78</v>
+        <v>79.23</v>
       </c>
     </row>
     <row r="50">
@@ -3514,26 +3514,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Nairne</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Luke</t>
+          <t>Distribution to Nairne (direct 0.5%)</t>
         </is>
       </c>
       <c r="G50" s="7" t="n">
-        <v>164.9</v>
+        <v>4904.6</v>
       </c>
     </row>
     <row r="51">
@@ -3544,26 +3544,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense (1099)</t>
+          <t>K-1 Distribution to Member</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1099-NEC payment to Issac</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>278.48</v>
+          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>79.23</v>
       </c>
     </row>
     <row r="52">
@@ -3574,26 +3574,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Contractor Labor — Chris</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Raj Duggal</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Distribution to Raj Duggal (direct 0.5%)</t>
+          <t>GP-paid expense: Chris</t>
         </is>
       </c>
       <c r="G52" s="7" t="n">
-        <v>79.23</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="53">
@@ -3604,26 +3604,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Professional Fees — TPA Admin</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>TPA (Formidium)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Distribution to Nairne (direct 0.5%)</t>
+          <t>GP-paid expense: TPA (Formidium)</t>
         </is>
       </c>
       <c r="G53" s="7" t="n">
-        <v>4904.6</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54">
@@ -3634,26 +3634,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member</t>
+          <t>Insurance Expense</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Distribution to Phil (direct 0.5%, K-1 partner per Nairne 2026-05-05)</t>
+          <t>GP-paid expense: Insurance</t>
         </is>
       </c>
       <c r="G54" s="7" t="n">
-        <v>79.23</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="55">
@@ -3669,198 +3669,108 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Contractor Labor — Chris</t>
+          <t>Professional Fees — TPA Admin</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>TPA (second line)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GP-paid expense: Chris</t>
+          <t>GP-paid expense: TPA (second line)</t>
         </is>
       </c>
       <c r="G55" s="7" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Professional Fees — TPA Admin</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TPA (Formidium)</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>GP-paid expense: TPA (Formidium)</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>600</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Insurance Expense</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>GP-paid expense: Insurance</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="n">
-        <v>18000</v>
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL TRANSACTIONS: 50</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Professional Fees — TPA Admin</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TPA (second line)</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>GP-paid expense: TPA (second line)</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>4500</v>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL DEBITS</t>
+        </is>
+      </c>
+      <c r="F58" s="21" t="n">
+        <v>153301.51</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL CREDITS</t>
+        </is>
+      </c>
+      <c r="G59" s="21" t="n">
+        <v>178341.11</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL TRANSACTIONS: 53</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL DEBITS</t>
-        </is>
-      </c>
-      <c r="F61" s="21" t="n">
-        <v>153301.51</v>
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>NET (Debit − Credit) = Net Income proxy: $-25,039.60</t>
+        </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL CREDITS</t>
-        </is>
-      </c>
-      <c r="G62" s="21" t="n">
-        <v>214341.1100000001</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="22" t="inlineStr">
-        <is>
-          <t>NET (Debit − Credit) = Net Income proxy: $-61,039.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="23" t="inlineStr">
+      <c r="A62" s="23" t="inlineStr">
         <is>
           <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Each row = one cash transaction. Revenue receipts are debits to Cash; distributions and expense payments are credits to Cash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>K-1 Distribution to Member: Nairne, Raj, Phil (all K-1 partners).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Capital Raiser Commission Expense: Alec, Jake, AJ, Issac, Luke (1099 contractors).</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>Each row = one cash transaction. Revenue receipts are debits to Cash; distributions and expense payments are credits to Cash.</t>
+          <t>Dates are end-of-month. Actual settlement may have been days/weeks later.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>K-1 Distribution to Member: Nairne, Raj, Phil (all K-1 partners).</t>
+          <t>Source: Distributions Armada Tech 2025 ledger + BEST ONE Dec 2025 Costs.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>Capital Raiser Commission Expense: Alec, Jake, AJ, Issac, Luke (1099 contractors).</t>
+          <t>TruQuant payments excluded entirely (per Nairne 2026-04-30).</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>Dates are end-of-month. Actual settlement may have been days/weeks later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>Source: Distributions Armada Tech 2025 ledger + BEST ONE Dec 2025 Costs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>TruQuant payments excluded entirely (per Nairne 2026-04-30).</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>Issac's December −$278.48 entry is a clawback against prior month overpayment.</t>
         </is>
@@ -3870,14 +3780,14 @@
   <mergeCells count="10">
     <mergeCell ref="A66:G66"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A70:G70"/>
     <mergeCell ref="A67:G67"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A69:G69"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A65:G65"/>
     <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A63:G63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3919,7 +3829,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-05</t>
+          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-07</t>
         </is>
       </c>
     </row>
@@ -4064,7 +3974,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>506c SPV Loan disbursements ($29,275 total) are NOT depreciable. They are loan receivables / equity investments — Balance Sheet items.</t>
+          <t>506c SPV Loan disbursements ($4,275 total) are NOT depreciable. They are loan receivables / equity investments — Balance Sheet items.</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4033,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-05</t>
+          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-07</t>
         </is>
       </c>
     </row>
@@ -4181,10 +4091,10 @@
         <v>34188.88</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>-24547.65245901639</v>
+        <v>10862.18360655738</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>14575.29836065574</v>
+        <v>25394.97049180328</v>
       </c>
       <c r="F8" s="12" t="inlineStr"/>
     </row>
@@ -4203,10 +4113,10 @@
         <v>946.97</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>-204.5637704918033</v>
+        <v>90.51819672131148</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>121.4608196721312</v>
+        <v>211.6247540983607</v>
       </c>
       <c r="F9" s="12" t="inlineStr"/>
     </row>
@@ -4225,10 +4135,10 @@
         <v>946.97</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>-204.5637704918033</v>
+        <v>90.51819672131148</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>121.4608196721312</v>
+        <v>211.6247540983607</v>
       </c>
       <c r="F10" s="12" t="inlineStr"/>
     </row>
@@ -4247,10 +4157,10 @@
         <v>36082.82</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>-24956.78</v>
+        <v>11043.22</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>14818.22</v>
+        <v>25818.22</v>
       </c>
       <c r="F11" s="9" t="n"/>
     </row>
@@ -4337,7 +4247,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-05</t>
+          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-07</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4556,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-05</t>
+          <t>Tax Year 2025  |  Period: Aug 1, 2025 – Dec 31, 2025  |  Generated 2026-05-07</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5022,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>

--- a/monily-package/Monily_Tax_Package_2025.xlsx
+++ b/monily-package/Monily_Tax_Package_2025.xlsx
@@ -184,7 +184,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -668,7 +670,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>HEADLINE NUMBERS</t>
+          <t>HEADLINE NUMBERS (Tax-Reclass Basis)</t>
         </is>
       </c>
     </row>
@@ -680,19 +682,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>GAAP-Basis ($)</t>
+          <t>Amount ($)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Tax-Reclass ($)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -703,10 +701,7 @@
       <c r="B15" s="7" t="n">
         <v>153023.03</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>153023.03</v>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>TPA-authoritative; Aug-Dec 2025</t>
         </is>
@@ -715,36 +710,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Less: 1099 Contractor Expenses (Alec, Jake, AJ, Issac, Luke)</t>
+          <t>Less: 1099 Contractor Expenses</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
         <v>-86754.81</v>
       </c>
-      <c r="C16" s="7" t="n">
-        <v>-86754.81</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Phil moved to K-1 per Nairne 2026-05-05</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Alec, Jake, AJ, Issac (Luke + Nikki &lt;$600 — no 1099 required, but still expense)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Less: Operating Expenses</t>
+          <t>Less: Operating Expenses (after reclass)</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>-55225</v>
-      </c>
-      <c r="C17" s="7" t="n">
         <v>-40450</v>
       </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Reclass moves $4,275 SPV loans to balance sheet, pro-rates Insurance</t>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Strips $4,275 SPV loan to balance sheet; pro-rates $18K Insurance to $7,500</t>
         </is>
       </c>
     </row>
@@ -755,21 +744,19 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>11043.22</v>
-      </c>
-      <c r="C18" s="10" t="n">
         <v>25818.22</v>
       </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Allocated to K-1 partners</t>
-        </is>
-      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Allocated to K-1 partners (Nairne, Raj, Phil)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>K-1 PARTNERS (3 partners)</t>
+          <t>K-1 PARTNERS (3 partners) — Per Nairne 2026-05-07: Fund Mgmt 59.5% split 50/50 between Nairne (K-1) and AJ (1099)</t>
         </is>
       </c>
     </row>
@@ -791,26 +778,26 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Allocated K-1 Income (Reclass-Basis, $)</t>
+          <t>Allocated K-1 Income ($)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Nairne (Fund Mgmt 59.5% + direct 0.5%)</t>
+          <t>Nairne (50%×Fund Mgmt 59.5% + direct 0.5% = 30.25% of perf fees)</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>98.36%</t>
+          <t>96.80%</t>
         </is>
       </c>
       <c r="C22" s="13" t="n">
         <v>34188.88</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>25394.97049180328</v>
+        <v>24992.03696</v>
       </c>
     </row>
     <row r="23">
@@ -821,14 +808,14 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
         <v>946.97</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>211.6247540983607</v>
+        <v>413.09152</v>
       </c>
     </row>
     <row r="24">
@@ -839,14 +826,14 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="C24" s="13" t="n">
         <v>946.97</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>211.6247540983607</v>
+        <v>413.09152</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +863,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Full Profit &amp; Loss with GAAP and Tax-Reclass columns, line-by-line detail</t>
+          <t>Profit &amp; Loss (Tax-Reclass basis), line-by-line detail</t>
         </is>
       </c>
     </row>
@@ -953,8 +940,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="25">
     <mergeCell ref="B11:D11"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="B29:D29"/>
@@ -962,6 +950,7 @@
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B6:D6"/>
@@ -970,11 +959,13 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B7:D7"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -986,13 +977,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1005,7 +996,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profit &amp; Loss Statement</t>
+          <t>Profit &amp; Loss Statement (Tax-Reclass Basis)</t>
         </is>
       </c>
     </row>
@@ -1024,19 +1015,15 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>GAAP-Style ($)</t>
+          <t>Amount ($)</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Tax-Reclass ($)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1054,10 +1041,7 @@
       <c r="B7" s="7" t="n">
         <v>153023.03</v>
       </c>
-      <c r="C7" s="7" t="n">
-        <v>153023.03</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Per TPA Reporting Packages, Performance Fees Crystallized line, Aug-Dec 2025.</t>
         </is>
@@ -1072,10 +1056,8 @@
       <c r="B8" s="15" t="n">
         <v>153023.03</v>
       </c>
-      <c r="C8" s="15" t="n">
-        <v>153023.03</v>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
+      <c r="C8" s="16" t="inlineStr"/>
+      <c r="D8" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1093,48 +1075,39 @@
       <c r="B11" s="7" t="n">
         <v>38076.87</v>
       </c>
-      <c r="C11" s="7" t="n">
-        <v>38076.87</v>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>1099-NEC issued separately</t>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>1099-NEC required (&gt;$600)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Jake Gordon</t>
+          <t xml:space="preserve">  AJ Affleck</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>10388.66</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>10388.66</v>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>1099-NEC issued separately</t>
+        <v>37139.89</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1099-NEC required (&gt;$600). Includes 50%×Fund Mgmt 59.5% + her 39%-pool consultant share per Nairne 2026-05-07.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AJ Affleck</t>
+          <t xml:space="preserve">  Jake Gordon</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>37139.89</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>37139.89</v>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>1099-NEC issued separately</t>
+        <v>10388.66</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>1099-NEC required (&gt;$600)</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1120,9 @@
       <c r="B14" s="7" t="n">
         <v>761.49</v>
       </c>
-      <c r="C14" s="7" t="n">
-        <v>761.49</v>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>1099-NEC issued separately</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>1099-NEC required (&gt;$600)</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1135,9 @@
       <c r="B15" s="7" t="n">
         <v>164.9</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>164.9</v>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>1099-NEC issued separately</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Less than $600 — NO 1099 required (still expense to GP)</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1150,9 @@
       <c r="B16" s="7" t="n">
         <v>223</v>
       </c>
-      <c r="C16" s="7" t="n">
-        <v>223</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>1099-NEC issued separately</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Less than $600 — NO 1099 required (still expense to GP)</t>
         </is>
       </c>
     </row>
@@ -1201,15 +1165,13 @@
       <c r="B17" s="15" t="n">
         <v>86754.81</v>
       </c>
-      <c r="C17" s="15" t="n">
-        <v>86754.81</v>
-      </c>
-      <c r="D17" s="16" t="inlineStr"/>
+      <c r="C17" s="16" t="inlineStr"/>
+      <c r="D17" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>OPERATING EXPENSES (Tax-Reclass)</t>
         </is>
       </c>
     </row>
@@ -1222,10 +1184,7 @@
       <c r="B20" s="7" t="n">
         <v>4000</v>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Issue 1099-NEC; verify SSN/address</t>
         </is>
@@ -1234,72 +1193,60 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Insurance (D&amp;O)</t>
+          <t xml:space="preserve">  Consulting (Nov)</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C21" s="7" t="n">
         <v>7500</v>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Reclass: $18k Dec is annual D&amp;O. Pro-rate to ~$7,500 for Aug-Dec period.</t>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Operating consulting; verify recipient for 1099</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PVD</t>
+          <t xml:space="preserve">  Insurance (D&amp;O)</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Vendor identification needed for 1099 obligation</t>
+        <v>7500</v>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Pro-rated: $18k Dec is annual D&amp;O — only 5/12 ($7,500) hits 2025; remaining $10,500 → Prepaid Asset on Balance Sheet</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Website</t>
+          <t xml:space="preserve">  PVD (Tech/Ads)</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Marketing/web build</t>
+        <v>6000</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Vendor identification needed for 1099 obligation</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ad Spend / Marketing</t>
+          <t xml:space="preserve">  Website</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Marketing</t>
+        <v>7500</v>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Marketing/web build</t>
         </is>
       </c>
     </row>
@@ -1312,10 +1259,7 @@
       <c r="B25" s="7" t="n">
         <v>2250</v>
       </c>
-      <c r="C25" s="7" t="n">
-        <v>2250</v>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Compliance/verification service</t>
         </is>
@@ -1330,310 +1274,360 @@
       <c r="B26" s="7" t="n">
         <v>5700</v>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>5700</v>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Verify GP-paid vs fund-paid (fund books also have $600/mo)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  506c SPV Loan</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>40450</v>
+      </c>
+      <c r="C27" s="16" t="inlineStr"/>
+      <c r="D27" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>RECLASSIFIED OFF P&amp;L (To Balance Sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  506c SPV Loan disbursement (Aug)</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
         <v>4275</v>
       </c>
-      <c r="C27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>RECLASS to Balance Sheet: $4,275 is a loan/capital item, not P&amp;L expense.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Total Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
-        <v>55225</v>
-      </c>
-      <c r="C28" s="15" t="n">
-        <v>40450</v>
-      </c>
-      <c r="D28" s="16" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>NET INCOME (Partnership)</t>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Loan receivable / equity investment — appears on Balance Sheet (Tab 3), NOT on P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Insurance prepaid portion (covers 2026)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>$10,500 of Dec $18K Insurance covers 2026 — booked as Prepaid Asset on Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>NET INCOME (Partnership)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B34" s="7" t="n">
         <v>153023.03</v>
       </c>
-      <c r="C31" s="7" t="n">
-        <v>153023.03</v>
-      </c>
-      <c r="D31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Less: Direct Costs (1099 contractors)</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
+      <c r="B35" s="7" t="n">
         <v>-86754.81</v>
       </c>
-      <c r="C32" s="7" t="n">
-        <v>-86754.81</v>
-      </c>
-      <c r="D32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Less: Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>-55225</v>
-      </c>
-      <c r="C33" s="7" t="n">
+      <c r="C35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Less: Operating Expenses (after reclass)</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
         <v>-40450</v>
       </c>
-      <c r="D33" s="8" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9">
+      <c r="C36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9">
         <f> NET INCOME</f>
         <v/>
       </c>
-      <c r="B34" s="10" t="n">
-        <v>11043.22</v>
-      </c>
-      <c r="C34" s="10" t="n">
+      <c r="B37" s="10" t="n">
         <v>25818.22</v>
       </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Tax-reclass column reflects accountant-preferred adjustments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>K-1 PARTNER ALLOCATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Nairne — Cash distributions received</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n">
-        <v>34188.88</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>34188.88</v>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>Includes Fund Mgmt 59.5% + direct 0.5%. K-1 capital account.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Nairne — Allocated share of Net Income (98.36%)</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n">
-        <v>10862.18360655738</v>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>25394.97049180328</v>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>K-1 Box 1 (Ordinary Income).</t>
-        </is>
-      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>This is what flows to Schedule K Line 1 → allocated to K-1 partners.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Raj Duggal — Cash distributions received</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>946.97</v>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>946.97</v>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>K-1 capital account.</t>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>K-1 PARTNER ALLOCATION (Per Nairne 2026-05-07: Fund Mgmt 59.5% split 50/50 between Nairne K-1 and AJ 1099)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Raj Duggal — Allocated share of Net Income (0.82%)</t>
+          <t>Nairne — Cash distributions received</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>90.51819672131148</v>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>211.6247540983607</v>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>K-1 Box 1.</t>
+        <v>34188.88</v>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Includes 50%×Fund Mgmt 59.5% + direct 0.5%. K-1 capital account.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Phil — Cash distributions received</t>
+          <t>Nairne — Allocated share of Net Income (96.80%)</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>946.97</v>
-      </c>
-      <c r="C41" s="7" t="n">
-        <v>946.97</v>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>K-1 capital account.</t>
+        <v>24992.03696</v>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>K-1 Box 1 (Ordinary Income). Ownership = 30.25/31.25 of partner share.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Phil — Allocated share of Net Income (0.82%)</t>
+          <t>Raj Duggal — Cash distributions received</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>90.51819672131148</v>
-      </c>
-      <c r="C42" s="7" t="n">
-        <v>211.6247540983607</v>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>K-1 Box 1.</t>
+        <v>946.97</v>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>K-1 capital account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Raj Duggal — Allocated share of Net Income (1.60%)</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>413.09152</v>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>K-1 Box 1. Ownership = 0.5/31.25 of partner share.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Phil — Cash distributions received</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>946.97</v>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>K-1 capital account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Phil — Allocated share of Net Income (1.60%)</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>413.09152</v>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>K-1 Box 1. Ownership = 0.5/31.25 of partner share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>PREPARER NOTES</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>1. Entity formed at the Armada Prime relaunch in August 2025; first year of operations.</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr"/>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2. Revenue source: TPA (Formidium) Performance Fees Crystallized line, Aug-Dec 2025.</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr"/>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>3. Member structure (per Nairne 2026-05-05): Nairne 60% (Fund Mgmt 59.5% + direct 0.5%), Raj Duggal 0.5%, Phil 0.5%. All three are K-1 partners.</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4. Phil was previously thought to be a 1099 contractor but has been corrected to K-1 partner status.</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr"/>
+          <t>1. Entity formed at the Armada Prime relaunch in August 2025; first year of operations.</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5. TruQuant payments are NOT included. The August 'Trader &amp; Developer' $6,909.93 + 'Spydr' $88.78 are excluded per 2026-04-30 policy decision (TQ is upstream of GP entity).</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr"/>
+          <t>2. Accounting method: ACCRUAL basis (recommended for tax minimization).</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6. Contractor amounts shown are CASH BASIS per Distributions Armada Tech 2025 ledger. Difference vs accrual basis (TPA Performance Fees Crystallized) ≈ $11,587.</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr"/>
+          <t>3. Revenue source: TPA (Formidium) Performance Fees Crystallized line, Aug-Dec 2025.</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7. RECOMMEND: $4,275 of '506c SPV Loan' line items should be reclassified to Balance Sheet (loan/capital).</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr"/>
+          <t>4. Member/economic structure (per Nairne 2026-05-07): Fund Mgmt 59.5% slice is split 50/50 between AJ Affleck (1099 contractor) and Nairne (K-1 partner). Plus 0.5% direct slices to each of Nairne, Raj, Phil. All three of Nairne/Raj/Phil are K-1 partners.</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8. RECOMMEND: $18,000 December Insurance line is likely annual D&amp;O — pro-rate to ~$7,500 for the 5-month period; book remainder as Prepaid Asset.</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr"/>
+          <t>5. AJ Affleck's 1099 amount thus includes BOTH her 39%-pool consultant share AND her 50%×Fund Mgmt 29.75% share.</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>6. K-1 ownership %: Nairne 30.25/31.25 = 96.80%; Raj 0.5/31.25 = 1.60%; Phil 0.5/31.25 = 1.60%. Total partner interest = 31.25% of pre-distribution gross.</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>7. TruQuant payments are NOT included. August 'Trader &amp; Developer' $6,909.93 + 'Spydr' $88.78 excluded per 2026-04-30 policy (TQ is upstream of GP entity).</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>8. RECOMMEND: $4,275 of August '506c SPV Loan' is a loan/capital item — reclassified to Balance Sheet.</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>9. RECOMMEND: $18,000 Dec Insurance line is annual D&amp;O — $7,500 pro-rated to 2025; remaining $10,500 booked as Prepaid Asset on Balance Sheet.</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10. 1099 threshold: contractors receiving &lt;$600/year (Luke $164.90, Nikki $223.00) do NOT require 1099-NEC issuance, but their amounts ARE still expense to GP entity.</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>11. K-1: NO threshold — partners receive K-1 every year regardless of dollar amount. Raj and Phil get K-1s even at $125 allocations.</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="50">
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C45:D45"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="C49:D49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1967,16 +1961,16 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>11043.22</v>
+        <v>25818.22</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>From P&amp;L Statement</t>
+          <t>From P&amp;L Statement (Tax-Reclass basis)</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>GAAP: $11,043.22. Reclass: $25,818.22</t>
+          <t>$25,818.22</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1981,7 @@
         </is>
       </c>
       <c r="B26" s="15" t="n">
-        <v>-25039.6</v>
+        <v>-10264.59999999999</v>
       </c>
       <c r="C26" s="14" t="inlineStr"/>
       <c r="D26" s="16" t="inlineStr"/>
@@ -2018,7 +2012,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>-25039.6</v>
+        <v>-10264.59999999999</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" s="8" t="inlineStr">
@@ -2034,7 +2028,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>39814.6</v>
+        <v>25039.59999999999</v>
       </c>
       <c r="C31" s="17" t="inlineStr"/>
       <c r="D31" s="18" t="inlineStr">
@@ -4005,7 +3999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4037,10 +4031,10 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>Per Nairne 2026-05-05: 3 K-1 partners — Nairne (60%), Raj Duggal (0.5%), Phil (0.5%). Phil corrected from prior 1099 status.</t>
+          <t>Per Nairne 2026-05-07: 3 K-1 partners. Fund Mgmt 59.5% slice is split 50/50 — half to AJ Affleck (1099 contractor) and half to Nairne (K-1). Plus direct 0.5% slices to Nairne, Raj, and Phil. Total partner economic interest = 31.25% of pre-distribution gross.</t>
         </is>
       </c>
     </row>
@@ -4052,22 +4046,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Ownership %</t>
+          <t>Economic Interest</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
+          <t>Ownership % (Normalized)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
           <t>Cash Distributions ($)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>K-1 Allocated Net Income — GAAP ($)</t>
-        </is>
-      </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>K-1 Allocated Net Income — Reclass ($)</t>
+          <t>K-1 Allocated Net Income ($)</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -4084,17 +4078,19 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>98.3607%</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="n">
+          <t>30.25% (= 50%×Fund Mgmt 59.5% + direct 0.5%)</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>96.80%</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
         <v>34188.88</v>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>10862.18360655738</v>
-      </c>
       <c r="E8" s="13" t="n">
-        <v>25394.97049180328</v>
+        <v>24992.03696</v>
       </c>
       <c r="F8" s="12" t="inlineStr"/>
     </row>
@@ -4106,17 +4102,19 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>0.8197%</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="n">
+          <t>0.50% (direct)</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
         <v>946.97</v>
       </c>
-      <c r="D9" s="13" t="n">
-        <v>90.51819672131148</v>
-      </c>
       <c r="E9" s="13" t="n">
-        <v>211.6247540983607</v>
+        <v>413.09152</v>
       </c>
       <c r="F9" s="12" t="inlineStr"/>
     </row>
@@ -4128,17 +4126,19 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>0.8197%</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="n">
+          <t>0.50% (direct)</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
         <v>946.97</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>90.51819672131148</v>
-      </c>
       <c r="E10" s="13" t="n">
-        <v>211.6247540983607</v>
+        <v>413.09152</v>
       </c>
       <c r="F10" s="12" t="inlineStr"/>
     </row>
@@ -4150,14 +4150,16 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
+          <t>31.25% partner / 68.75% non-partner</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
           <t>100.00%</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="D11" s="10" t="n">
         <v>36082.82</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>11043.22</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>25818.22</v>
@@ -4174,39 +4176,55 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Nairne's 60% is the sum of Fund Management 59.5% slice + direct 0.5% slice. Both are partner allocations (K-1), not entity expenses.</t>
+          <t>Per Nairne 2026-05-07: the 59.5% Fund Management slice is split 50/50 between AJ Affleck (1099 contractor) and Nairne (K-1 partner). AJ's $37,139.89 in 2025 1099 income includes BOTH her 39%-pool consultant share AND her 50%×Fund Mgmt share.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Cash Distributions and Allocated K-1 Income are different concepts in partnership tax. K-1 Box 1 reports allocated income; Box L tracks capital account changes from distributions.</t>
+          <t>Nairne's K-1 economic interest is 30.25% of pre-distribution gross (= 50%×59.5% + 0.5% direct).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Ownership % shown is derived from the 60/0.5/0.5 split. The actual LLC operating agreement governs the legal allocation.</t>
+          <t>Total K-1 partner interest = 31.25% (Nairne 30.25 + Raj 0.5 + Phil 0.5). Normalized partner ownership: Nairne 96.80%, Raj 1.60%, Phil 1.60%.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>If the operating agreement specifies a different income allocation method (e.g., guaranteed payments to Nairne for managing), the accountant should adjust.</t>
+          <t>Cash Distributions and Allocated K-1 Income are different concepts in partnership tax. K-1 Box 1 reports allocated income (taxable to partner); Box L tracks capital account changes from cash distributions (NOT additionally taxed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>K-1 issuance: ALL partners receive a K-1 every year regardless of dollar amount — even tiny allocations like Raj's $125 require a K-1. There is no $600 threshold for K-1s (unlike 1099s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>The actual LLC operating agreement governs the legal allocation. Confirm with accountant before filing.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
@@ -4220,14 +4238,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4264,17 +4282,17 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
+          <t>1099-NEC Required?</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
           <t>Source of Payment</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>EIN/SSN (fill in)</t>
-        </is>
-      </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Address (fill in)</t>
+          <t>EIN/SSN + Address (fill in)</t>
         </is>
       </c>
     </row>
@@ -4289,161 +4307,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
           <t>Capital raiser commission (39% of his investors' perf fees)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>10388.66</v>
+        <v>37139.89</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Capital raiser commission</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Capital raiser commission + 50%×Fund Mgmt 59.5% (per Nairne 2026-05-07)</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>37139.89</v>
+        <v>10388.66</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
           <t>Capital raiser commission</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Issac Morris</t>
+          <t>Chris (last name TBD)</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>761.49</v>
+        <v>11500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Capital raiser commission</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Operating contractor labor (Nov $7,500 + Dec $4,000)</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Issac Morris</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>761.49</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Capital raiser commission</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Nikki (last name TBD)</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>223</v>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>NO (&lt;$600 threshold)</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Capital raiser commission (Nov 2025 only) — under $600</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
           <t>Luke Affleck</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B12" s="19" t="n">
         <v>164.9</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Capital raiser commission</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Nikki (last name TBD)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>223</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Capital raiser commission (Nov 2025 only)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Chris (last name TBD)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>11500</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Operating contractor labor (Nov $7,500 + Dec $4,000)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>NO (&lt;$600 threshold)</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Capital raiser commission (Dec 2025 only) — under $600</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL 1099 PAYMENTS</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL — All Contractor Payments (P&amp;L expense)</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
         <v>98254.81</v>
       </c>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL — 1099-NEC Forms Required to Issue</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>97866.91</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>(only contractors &gt;$600)</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>VENDORS THAT MAY ALSO REQUIRE 1099</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>If individual/sole prop and &gt;$600 → 1099-NEC. Verify entity type.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ad Spend / Marketing vendors</t>
+          <t>PVD (Tech/Ads)</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>If individual/sole prop. Verify.</t>
+        <v>6000</v>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>If individual/sole prop and &gt;$600 → 1099-NEC. Verify entity type.</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4504,7 @@
       <c r="B18" s="7" t="n">
         <v>7500</v>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>If individual contractor. Verify.</t>
         </is>
@@ -4471,7 +4519,7 @@
       <c r="B19" s="7" t="n">
         <v>2250</v>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Likely corporate; unlikely 1099 needed. Verify.</t>
         </is>
@@ -4486,7 +4534,7 @@
       <c r="B20" s="7" t="n">
         <v>18000</v>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Corporate — no 1099.</t>
         </is>
@@ -4501,24 +4549,71 @@
       <c r="B21" s="7" t="n">
         <v>5700</v>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Corporate — no 1099.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>NOTE: Phil is NOT on this 1099 list — Phil is a K-1 partner (per Nairne 2026-05-05). See K-1 Partners tab.</t>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Consulting (Nov)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Verify recipient identity for 1099 requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>1099-NEC threshold: $600/year per recipient. Below that, NO 1099 required (but still expense to GP entity).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Luke ($164.90) and Nikki ($223.00) are under $600 — no 1099-NEC issuance required for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Phil is NOT on this 1099 list — Phil is a K-1 partner (per Nairne 2026-05-05). See K-1 Partners tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>AJ Affleck IS a 1099 contractor (NOT a K-1 partner). Her $37,139.89 includes BOTH her 39%-pool consultant share AND her 50%×Fund Mgmt 59.5% share (per Nairne 2026-05-07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>All 1099-NECs must be furnished to recipients by January 31 of the following year.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/monily-package/Monily_Tax_Package_2025.xlsx
+++ b/monily-package/Monily_Tax_Package_2025.xlsx
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -187,6 +187,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -553,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -756,7 +757,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>K-1 PARTNERS (3 partners) — Per Nairne 2026-05-07: Fund Mgmt 59.5% split 50/50 between Nairne (K-1) and AJ (1099)</t>
+          <t>K-1 PARTNERS — Income Allocation (per commission structure, NOT 90/5/5 voting rights)</t>
         </is>
       </c>
     </row>
@@ -768,7 +769,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Ownership %</t>
+          <t>Income Share % (commission)</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -778,14 +779,14 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Allocated K-1 Income ($)</t>
+          <t>K-1 Box 1 Income ($)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Nairne (50%×Fund Mgmt 59.5% + direct 0.5% = 30.25% of perf fees)</t>
+          <t>Nairne (50%×Mgmt 59.5% + 0.5% direct = 30.25% economic)</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -803,7 +804,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Raj Duggal (direct 0.5%)</t>
+          <t>Raj Duggal (0.5% direct)</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
@@ -821,7 +822,7 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Phil (direct 0.5%)</t>
+          <t>Phil (0.5% direct)</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
@@ -836,111 +837,118 @@
         <v>413.09152</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>(LLC voting/decision-making is 90/5/5 — separate from income allocation above)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>TAB GUIDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>1. Cover &amp; Summary</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>This tab — entity info, headline numbers, K-1 partner allocations, file overview</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2. P&amp;L Statement</t>
+          <t>1. Cover &amp; Summary</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Profit &amp; Loss (Tax-Reclass basis), line-by-line detail</t>
+          <t>This tab — entity info, headline numbers, K-1 partner allocations, file overview</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3. Balance Sheet</t>
+          <t>2. P&amp;L Statement</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>As of Dec 31, 2025. Best-effort with placeholders flagged for accountant</t>
+          <t>Profit &amp; Loss (Tax-Reclass basis), line-by-line detail</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>4. General Ledger</t>
+          <t>3. Balance Sheet</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Transaction-level ledger of all cash movements (revenue, distributions, expenses)</t>
+          <t>As of Dec 31, 2025. Best-effort with placeholders flagged for accountant</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>5. Asset Schedule</t>
+          <t>4. General Ledger</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Fixed asset / depreciation schedule. No fixed assets recorded.</t>
+          <t>Transaction-level ledger of all cash movements (revenue, distributions, expenses)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>6. K-1 Partners</t>
+          <t>5. Asset Schedule</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Detailed partner schedule for K-1 prep (Nairne, Raj, Phil)</t>
+          <t>Fixed asset / depreciation schedule. No fixed assets recorded.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>7. 1099 Recipients</t>
+          <t>6. K-1 Partners</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Detailed contractor schedule for 1099-NEC prep</t>
+          <t>Detailed partner schedule for K-1 prep (Nairne, Raj, Phil)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>7. 1099 Recipients</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Detailed contractor schedule for 1099-NEC prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>8. Tax Organizer Answers</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Pre-filled answers for the Monily Partnership Tax Organizer form</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B8:D8"/>
@@ -958,12 +966,13 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
   </mergeCells>
@@ -3999,7 +4008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4031,10 +4040,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="75" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>Per Nairne 2026-05-07: 3 K-1 partners. Fund Mgmt 59.5% slice is split 50/50 — half to AJ Affleck (1099 contractor) and half to Nairne (K-1). Plus direct 0.5% slices to Nairne, Raj, and Phil. Total partner economic interest = 31.25% of pre-distribution gross.</t>
+          <t>Per Nairne 2026-05-07: K-1 income is allocated by the COMMISSION/INCOME STRUCTURE (not by 90/5/5 LLC voting rights). Income flows: 59.5% Management (split 50/50 between Nairne K-1 and AJ 1099) + 39% to capital-raiser contractors (1099, by investor) + 0.5% each to Nairne, Raj, Phil. Partners (Nairne 30.25% + Raj 0.5% + Phil 0.5% = 31.25% total) get K-1s. The 90/5/5 LLC ownership governs voting/decision-making, NOT income allocation.</t>
         </is>
       </c>
     </row>
@@ -4046,22 +4055,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Economic Interest</t>
+          <t>Income Source (per commission)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Ownership % (Normalized)</t>
+          <t>Income Share %</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Cash Distributions ($)</t>
+          <t>Cash Distributions Received ($)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>K-1 Allocated Net Income ($)</t>
+          <t>K-1 Box 1 Income ($)</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -4078,7 +4087,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>30.25% (= 50%×Fund Mgmt 59.5% + direct 0.5%)</t>
+          <t>50%×Mgmt 59.5% + 0.5% direct = 30.25% pre-distribution</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -4102,7 +4111,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>0.50% (direct)</t>
+          <t>0.5% direct</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -4126,7 +4135,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>0.50% (direct)</t>
+          <t>0.5% direct</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -4145,17 +4154,13 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>31.25% partner / 68.75% non-partner</t>
-        </is>
-      </c>
+          <t>TOTAL (partners only — non-partner contractors get 1099s, not K-1s)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>100% partner share</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
@@ -4167,66 +4172,173 @@
       <c r="F11" s="9" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>CAPITAL ACCOUNT ANALYSIS (per partner)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>K-1 Box 1 Income (+ to capital)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Cash Distributions (− from capital)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Net Capital Change</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nairne</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>24992.03696</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>-34188.88</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>-9196.843039999996</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Capital decreases</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Raj Duggal</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>413.09152</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>-946.97</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>-533.8784800000001</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Capital decreases</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Phil</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>413.09152</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>-946.97</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>-533.8784800000001</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Capital decreases</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Per Nairne 2026-05-07: the 59.5% Fund Management slice is split 50/50 between AJ Affleck (1099 contractor) and Nairne (K-1 partner). AJ's $37,139.89 in 2025 1099 income includes BOTH her 39%-pool consultant share AND her 50%×Fund Mgmt share.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Nairne's K-1 economic interest is 30.25% of pre-distribution gross (= 50%×59.5% + 0.5% direct).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Total K-1 partner interest = 31.25% (Nairne 30.25 + Raj 0.5 + Phil 0.5). Normalized partner ownership: Nairne 96.80%, Raj 1.60%, Phil 1.60%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Cash Distributions and Allocated K-1 Income are different concepts in partnership tax. K-1 Box 1 reports allocated income (taxable to partner); Box L tracks capital account changes from cash distributions (NOT additionally taxed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>K-1 issuance: ALL partners receive a K-1 every year regardless of dollar amount — even tiny allocations like Raj's $125 require a K-1. There is no $600 threshold for K-1s (unlike 1099s).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>The actual LLC operating agreement governs the legal allocation. Confirm with accountant before filing.</t>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>TWO SEPARATE CONCEPTS: (a) LLC OWNERSHIP / VOTING = 90/5/5 (Nairne/Raj/Phil) — controls decision-making. (b) INCOME ALLOCATION = commission structure (Nairne 30.25% / Raj 0.5% / Phil 0.5% = 31.25% total partner) — controls K-1 Box 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>The operating agreement specifies the income allocation as a 'special allocation' that must have substantial economic effect under IRS regs §1.704-1(b). The accountant should confirm this is properly documented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>AJ Affleck is NOT a partner — she's a 1099 contractor. Her 50%×Fund Mgmt 59.5% share is contractor income, not a partner allocation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Nairne's cash distributions ($34,189) exceed her K-1 income allocation ($24,992). The excess $9,197 reduces her capital account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Raj/Phil's cash distributions ($947 each) exceed their K-1 income allocations ($413 each). The excess $534 each reduces their capital accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>K-1 issuance: ALL partners receive a K-1 every year regardless of dollar amount. No $600 threshold (unlike 1099s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>If a partner's capital account goes negative at year-end, the accountant may need to: (a) document initial capital contributions at formation, (b) reclassify excess distributions as Guaranteed Payments (Form 1065 Line 10), or (c) treat as a partner loan. The operating agreement governs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4687,7 +4799,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>EIN</t>
         </is>
@@ -4700,7 +4812,7 @@
       <c r="C8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Phone Number</t>
         </is>
@@ -4713,7 +4825,7 @@
       <c r="C9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
@@ -4726,7 +4838,7 @@
       <c r="C10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Corporation address / State / City / Zip / Country</t>
         </is>
@@ -4763,7 +4875,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Partnership state residence</t>
         </is>
@@ -4958,7 +5070,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>Foreign account interest/signature authority</t>
         </is>
